--- a/code/output/model_output/apollo/vehicle/0_vehicle_model_combine_output.xlsx
+++ b/code/output/model_output/apollo/vehicle/0_vehicle_model_combine_output.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xnw17/Documents/GitHub/Conjoint_Survey_25/code/output/model_output/apollo/vehicle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6A083E-C5E8-5941-AD21-C6B7DED4E676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{337E903F-3FC8-C547-8A00-F176DA73D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="260" yWindow="1040" windowWidth="28880" windowHeight="17000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2440" yWindow="8820" windowWidth="28880" windowHeight="17000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pref_1class" sheetId="6" r:id="rId1"/>
@@ -526,7 +526,7 @@
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -722,7 +722,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -889,7 +889,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1639,18 +1638,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B5AC401-21AB-DC45-B3FA-02B41EDD9230}">
   <dimension ref="A1:I34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" style="26" customWidth="1"/>
     <col min="2" max="16384" width="10.83203125" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="67" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="16" customHeight="1">
       <c r="B2" s="26" t="s">
         <v>83</v>
       </c>
@@ -1673,7 +1672,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>133</v>
       </c>
@@ -1703,7 +1702,7 @@
         <v>-5.8350257970086181</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9">
       <c r="A4" s="26" t="s">
         <v>114</v>
       </c>
@@ -1733,7 +1732,7 @@
         <v>-2.4819885390411764</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5" s="26" t="s">
         <v>115</v>
       </c>
@@ -1763,7 +1762,7 @@
         <v>-0.43977736997649758</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9">
       <c r="A6" s="26" t="s">
         <v>116</v>
       </c>
@@ -1793,7 +1792,7 @@
         <v>0.49936891019609503</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9">
       <c r="A7" s="26" t="s">
         <v>117</v>
       </c>
@@ -1823,7 +1822,7 @@
         <v>-0.20441204250829936</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9">
       <c r="A8" s="26" t="s">
         <v>118</v>
       </c>
@@ -1853,7 +1852,7 @@
         <v>-0.10699380218909969</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9">
       <c r="A9" s="26" t="s">
         <v>119</v>
       </c>
@@ -1883,7 +1882,7 @@
         <v>-0.82726307166411928</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9">
       <c r="A10" s="26" t="s">
         <v>120</v>
       </c>
@@ -1909,12 +1908,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9">
       <c r="A13" s="67" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9">
       <c r="B14" s="26" t="s">
         <v>83</v>
       </c>
@@ -1937,7 +1936,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9">
       <c r="A15" s="26" t="s">
         <v>113</v>
       </c>
@@ -1967,7 +1966,7 @@
         <v>-7.1134025162614769</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9">
       <c r="A16" s="26" t="s">
         <v>114</v>
       </c>
@@ -1997,7 +1996,7 @@
         <v>-2.9255206679995869</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9">
       <c r="A17" s="26" t="s">
         <v>115</v>
       </c>
@@ -2027,7 +2026,7 @@
         <v>-0.21265862055045123</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9">
       <c r="A18" s="26" t="s">
         <v>116</v>
       </c>
@@ -2057,7 +2056,7 @@
         <v>0.50142311692787622</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9">
       <c r="A19" s="26" t="s">
         <v>117</v>
       </c>
@@ -2087,7 +2086,7 @@
         <v>-0.35126356891015237</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9">
       <c r="A20" s="26" t="s">
         <v>118</v>
       </c>
@@ -2117,7 +2116,7 @@
         <v>-0.14753098306707865</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9">
       <c r="A21" s="26" t="s">
         <v>119</v>
       </c>
@@ -2147,7 +2146,7 @@
         <v>-0.77057717746683796</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9">
       <c r="A22" s="26" t="s">
         <v>120</v>
       </c>
@@ -2173,7 +2172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="16">
       <c r="B27" s="77" t="s">
         <v>34</v>
       </c>
@@ -2184,7 +2183,7 @@
       <c r="G27" s="77"/>
       <c r="H27" s="77"/>
     </row>
-    <row r="28" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="17">
       <c r="B28" s="6" t="s">
         <v>42</v>
       </c>
@@ -2207,7 +2206,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="42" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="42">
       <c r="B29" s="9"/>
       <c r="C29" s="8"/>
       <c r="D29" s="9"/>
@@ -2224,7 +2223,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9">
       <c r="B30" s="9"/>
       <c r="C30" s="8"/>
       <c r="D30" s="9"/>
@@ -2233,7 +2232,7 @@
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="16">
       <c r="A31" s="26" t="s">
         <v>102</v>
       </c>
@@ -2259,7 +2258,7 @@
         <v>-0.82726310000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9">
       <c r="A32" s="26" t="s">
         <v>103</v>
       </c>
@@ -2285,12 +2284,12 @@
         <v>-0.77057719999999996</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:8">
       <c r="E33" s="66"/>
       <c r="G33" s="19"/>
       <c r="H33" s="19"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:8">
       <c r="B34" s="19"/>
       <c r="C34" s="19"/>
       <c r="D34" s="19"/>
@@ -2310,18 +2309,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FAF559C-1D3C-3348-B1FD-69C9536248D3}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" style="26" customWidth="1"/>
     <col min="2" max="16384" width="10.83203125" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" s="67" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" customHeight="1">
       <c r="B2" s="26" t="s">
         <v>83</v>
       </c>
@@ -2344,7 +2343,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="A3" s="26" t="s">
         <v>113</v>
       </c>
@@ -2370,7 +2369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8">
       <c r="A4" s="26" t="s">
         <v>127</v>
       </c>
@@ -2396,7 +2395,7 @@
         <v>4.7124082414029499E-11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8">
       <c r="A5" s="26" t="s">
         <v>128</v>
       </c>
@@ -2422,7 +2421,7 @@
         <v>9.9597042519006295E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8">
       <c r="A6" s="26" t="s">
         <v>129</v>
       </c>
@@ -2448,7 +2447,7 @@
         <v>4.9431530366070798E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8">
       <c r="A7" s="26" t="s">
         <v>130</v>
       </c>
@@ -2474,7 +2473,7 @@
         <v>6.3152191920323704E-8</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8">
       <c r="A8" s="26" t="s">
         <v>131</v>
       </c>
@@ -2500,7 +2499,7 @@
         <v>1.9509192683564399E-7</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8">
       <c r="A9" s="26" t="s">
         <v>132</v>
       </c>
@@ -2526,7 +2525,7 @@
         <v>8.0853415074244595E-9</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8">
       <c r="A10" s="26" t="s">
         <v>121</v>
       </c>
@@ -2552,12 +2551,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8">
       <c r="A13" s="67" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8">
       <c r="B14" s="26" t="s">
         <v>83</v>
       </c>
@@ -2580,7 +2579,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8">
       <c r="A15" s="26" t="s">
         <v>113</v>
       </c>
@@ -2606,7 +2605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8">
       <c r="A16" s="26" t="s">
         <v>127</v>
       </c>
@@ -2632,7 +2631,7 @@
         <v>7.6542137517066106E-8</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="26" t="s">
         <v>128</v>
       </c>
@@ -2658,7 +2657,7 @@
         <v>0.13865032162449101</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="26" t="s">
         <v>129</v>
       </c>
@@ -2684,7 +2683,7 @@
         <v>3.5998133347045999E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="26" t="s">
         <v>130</v>
       </c>
@@ -2710,7 +2709,7 @@
         <v>2.22510898595374E-12</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="26" t="s">
         <v>131</v>
       </c>
@@ -2736,7 +2735,7 @@
         <v>4.8441761713036199E-10</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="26" t="s">
         <v>132</v>
       </c>
@@ -2762,7 +2761,7 @@
         <v>4.3286826210131596E-6</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" s="26" t="s">
         <v>121</v>
       </c>
@@ -2788,19 +2787,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="B24" s="26">
         <f>B3/B10</f>
         <v>-5.8350334140072482</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="B25" s="26">
         <f>B15/B22</f>
         <v>-7.113391106224122</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="16">
       <c r="B27" s="77" t="s">
         <v>34</v>
       </c>
@@ -2811,7 +2810,7 @@
       <c r="G27" s="77"/>
       <c r="H27" s="77"/>
     </row>
-    <row r="28" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="17">
       <c r="B28" s="6" t="s">
         <v>42</v>
       </c>
@@ -2834,7 +2833,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="42">
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -2851,7 +2850,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -2860,7 +2859,7 @@
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="16">
       <c r="A31" s="26" t="s">
         <v>102</v>
       </c>
@@ -2889,7 +2888,7 @@
         <v>-5.8350257970086181</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="26" t="s">
         <v>103</v>
       </c>
@@ -2918,12 +2917,11 @@
         <v>-7.1134025162614769</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="E33" s="80"/>
+    <row r="33" spans="2:8">
       <c r="G33" s="19"/>
       <c r="H33" s="19"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:8">
       <c r="B34" s="19"/>
       <c r="C34" s="19"/>
       <c r="D34" s="19"/>
@@ -2944,14 +2942,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="11" max="11" width="21.1640625" customWidth="1"/>
     <col min="18" max="20" width="8.83203125" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="24">
       <c r="A1" s="46" t="s">
         <v>102</v>
       </c>
@@ -2959,7 +2957,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18">
       <c r="A2" s="26"/>
       <c r="B2" s="26" t="s">
         <v>83</v>
@@ -3005,7 +3003,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18">
       <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
@@ -3055,7 +3053,7 @@
         <v>9.7309081814600496E-7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18">
       <c r="A4" s="26" t="s">
         <v>1</v>
       </c>
@@ -3105,7 +3103,7 @@
         <v>1.99945656745637E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18">
       <c r="A5" s="26" t="s">
         <v>2</v>
       </c>
@@ -3155,7 +3153,7 @@
         <v>2.5738827960486402E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18">
       <c r="A6" s="26" t="s">
         <v>3</v>
       </c>
@@ -3205,7 +3203,7 @@
         <v>2.52246528512787E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18">
       <c r="A7" s="26" t="s">
         <v>4</v>
       </c>
@@ -3255,7 +3253,7 @@
         <v>1.23442339687949E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18">
       <c r="A8" s="26" t="s">
         <v>5</v>
       </c>
@@ -3305,7 +3303,7 @@
         <v>7.8374105737521998E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18">
       <c r="A9" s="26" t="s">
         <v>6</v>
       </c>
@@ -3355,7 +3353,7 @@
         <v>5.7380340461898904E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18">
       <c r="A10" s="26" t="s">
         <v>7</v>
       </c>
@@ -3405,7 +3403,7 @@
         <v>1.4437543389256299E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18">
       <c r="A11" s="26" t="s">
         <v>8</v>
       </c>
@@ -3455,7 +3453,7 @@
         <v>6.0992988437647E-11</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18">
       <c r="A12" s="26" t="s">
         <v>9</v>
       </c>
@@ -3505,7 +3503,7 @@
         <v>0.639483597759397</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18">
       <c r="A13" s="26" t="s">
         <v>10</v>
       </c>
@@ -3555,7 +3553,7 @@
         <v>1.7298111409935799E-7</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18">
       <c r="A14" s="26" t="s">
         <v>11</v>
       </c>
@@ -3605,7 +3603,7 @@
         <v>0.305538743697302</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18">
       <c r="A15" s="26" t="s">
         <v>12</v>
       </c>
@@ -3655,7 +3653,7 @@
         <v>7.31428727880568E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18">
       <c r="A16" s="26" t="s">
         <v>13</v>
       </c>
@@ -3705,7 +3703,7 @@
         <v>2.9355465688169998E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18">
       <c r="A17" s="26" t="s">
         <v>14</v>
       </c>
@@ -3755,7 +3753,7 @@
         <v>4.3992805522008498E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18">
       <c r="A18" s="26" t="s">
         <v>15</v>
       </c>
@@ -3805,7 +3803,7 @@
         <v>2.6443770062556399E-8</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18">
       <c r="A19" s="26" t="s">
         <v>22</v>
       </c>
@@ -3855,7 +3853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18">
       <c r="A20" s="26" t="s">
         <v>23</v>
       </c>
@@ -3905,7 +3903,7 @@
         <v>3.6723041368702498E-5</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18">
       <c r="A21" s="26" t="s">
         <v>24</v>
       </c>
@@ -3955,7 +3953,7 @@
         <v>0.23998815478865199</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18">
       <c r="A22" s="26" t="s">
         <v>25</v>
       </c>
@@ -4005,7 +4003,7 @@
         <v>0.48143563174861997</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18">
       <c r="A23" s="26" t="s">
         <v>26</v>
       </c>
@@ -4055,7 +4053,7 @@
         <v>4.8559727350294704E-9</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18">
       <c r="A24" s="26" t="s">
         <v>27</v>
       </c>
@@ -4105,7 +4103,7 @@
         <v>2.59280922785932E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18">
       <c r="A25" s="26" t="s">
         <v>28</v>
       </c>
@@ -4155,7 +4153,7 @@
         <v>0.321914053457242</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18">
       <c r="A26" s="26" t="s">
         <v>29</v>
       </c>
@@ -4205,7 +4203,7 @@
         <v>3.1927571697565301E-11</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18">
       <c r="A27" s="26" t="s">
         <v>16</v>
       </c>
@@ -4255,7 +4253,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18">
       <c r="A28" s="26" t="s">
         <v>17</v>
       </c>
@@ -4305,7 +4303,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18">
       <c r="A29" s="26" t="s">
         <v>18</v>
       </c>
@@ -4355,7 +4353,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18">
       <c r="A30" s="26" t="s">
         <v>71</v>
       </c>
@@ -4405,7 +4403,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18">
       <c r="A31" s="26" t="s">
         <v>90</v>
       </c>
@@ -4455,7 +4453,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18">
       <c r="A32" s="26" t="s">
         <v>91</v>
       </c>
@@ -4505,7 +4503,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18">
       <c r="A33" s="26" t="s">
         <v>92</v>
       </c>
@@ -4555,7 +4553,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18">
       <c r="A34" s="26" t="s">
         <v>93</v>
       </c>
@@ -4605,7 +4603,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18">
       <c r="A35" s="26" t="s">
         <v>19</v>
       </c>
@@ -4655,7 +4653,7 @@
         <v>0.36965656458838297</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18">
       <c r="A36" s="26" t="s">
         <v>20</v>
       </c>
@@ -4705,7 +4703,7 @@
         <v>5.4024935891572304E-6</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18">
       <c r="A37" s="26" t="s">
         <v>21</v>
       </c>
@@ -4755,7 +4753,7 @@
         <v>0.44341707738672698</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18">
       <c r="A38" s="26" t="s">
         <v>72</v>
       </c>
@@ -4805,7 +4803,7 @@
         <v>4.1727130896959098E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18">
       <c r="A39" s="26" t="s">
         <v>94</v>
       </c>
@@ -4855,7 +4853,7 @@
         <v>0.86019547104338201</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18">
       <c r="A40" s="26" t="s">
         <v>95</v>
       </c>
@@ -4905,7 +4903,7 @@
         <v>2.2198185667826598E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18">
       <c r="A41" s="26" t="s">
         <v>96</v>
       </c>
@@ -4955,7 +4953,7 @@
         <v>0.173061346374841</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18">
       <c r="A42" s="26" t="s">
         <v>97</v>
       </c>
@@ -5005,7 +5003,7 @@
         <v>9.2294271897064295E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18">
       <c r="A43" s="26" t="s">
         <v>30</v>
       </c>
@@ -5055,7 +5053,7 @@
         <v>0.14138501593751199</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18">
       <c r="A44" s="26" t="s">
         <v>31</v>
       </c>
@@ -5105,7 +5103,7 @@
         <v>0.83509184471389397</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18">
       <c r="A45" s="26" t="s">
         <v>32</v>
       </c>
@@ -5155,7 +5153,7 @@
         <v>0.72785799491410197</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18">
       <c r="A46" s="26" t="s">
         <v>98</v>
       </c>
@@ -5205,7 +5203,7 @@
         <v>0.37428958883591901</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18">
       <c r="A47" s="26" t="s">
         <v>73</v>
       </c>
@@ -5255,7 +5253,7 @@
         <v>9.7131059576570894E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18">
       <c r="A48" s="26" t="s">
         <v>99</v>
       </c>
@@ -5305,7 +5303,7 @@
         <v>5.8515655423800203E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18">
       <c r="A49" s="26" t="s">
         <v>100</v>
       </c>
@@ -5355,7 +5353,7 @@
         <v>1.1529022206937699E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18">
       <c r="A50" s="26" t="s">
         <v>101</v>
       </c>
@@ -5437,15 +5435,17 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:AE25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AE32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.1640625" style="17" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="17"/>
     <col min="3" max="3" width="10.83203125" style="18"/>
     <col min="4" max="4" width="10.83203125" style="20"/>
     <col min="5" max="5" width="27.83203125" style="24" customWidth="1"/>
-    <col min="6" max="17" width="10.83203125" style="17"/>
+    <col min="6" max="14" width="10.83203125" style="17"/>
+    <col min="15" max="15" width="0" style="17" hidden="1" customWidth="1"/>
+    <col min="16" max="17" width="10.83203125" style="17"/>
     <col min="18" max="18" width="5.5" style="17" customWidth="1"/>
     <col min="19" max="21" width="10.83203125" style="17"/>
     <col min="22" max="25" width="16.1640625" style="24" customWidth="1"/>
@@ -5456,7 +5456,7 @@
     <col min="31" max="16384" width="10.83203125" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="7" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" s="7" customFormat="1" ht="41" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:31" s="7" customFormat="1" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" s="7" customFormat="1" ht="68" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>38</v>
       </c>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="AD2" s="48"/>
     </row>
-    <row r="3" spans="1:31" s="8" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" s="8" customFormat="1" ht="40" customHeight="1">
       <c r="B3" s="9"/>
       <c r="C3" s="10"/>
       <c r="D3" s="11"/>
@@ -5612,7 +5612,7 @@
       <c r="AC3" s="9"/>
       <c r="AD3" s="49"/>
     </row>
-    <row r="4" spans="1:31" s="8" customFormat="1" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" s="8" customFormat="1" ht="40" hidden="1" customHeight="1">
       <c r="B4" s="9"/>
       <c r="C4" s="10"/>
       <c r="D4" s="11"/>
@@ -5634,7 +5634,7 @@
       <c r="AC4" s="9"/>
       <c r="AD4" s="49"/>
     </row>
-    <row r="5" spans="1:31" s="13" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" s="13" customFormat="1" ht="34" hidden="1">
       <c r="A5" s="12" t="s">
         <v>50</v>
       </c>
@@ -5689,7 +5689,7 @@
       <c r="AC5" s="16"/>
       <c r="AD5" s="50"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31">
       <c r="A6" s="30" t="s">
         <v>102</v>
       </c>
@@ -5716,7 +5716,7 @@
       <c r="X6" s="40"/>
       <c r="Y6" s="40"/>
     </row>
-    <row r="7" spans="1:31" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" ht="70" customHeight="1">
       <c r="A7" s="78" t="s">
         <v>104</v>
       </c>
@@ -5809,7 +5809,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" ht="65" customHeight="1">
       <c r="A8" s="78"/>
       <c r="B8" s="12" t="s">
         <v>60</v>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="AE8" s="79"/>
     </row>
-    <row r="9" spans="1:31" ht="78" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" ht="78" customHeight="1">
       <c r="A9" s="78"/>
       <c r="B9" s="12" t="s">
         <v>61</v>
@@ -5993,10 +5993,10 @@
       </c>
       <c r="AE9" s="79"/>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31">
       <c r="N10" s="19"/>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31">
       <c r="A11" s="30" t="s">
         <v>103</v>
       </c>
@@ -6015,7 +6015,7 @@
       <c r="AB11" s="59"/>
       <c r="AC11" s="39"/>
     </row>
-    <row r="12" spans="1:31" ht="32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" ht="32">
       <c r="A12" s="78" t="s">
         <v>104</v>
       </c>
@@ -6107,7 +6107,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="48" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" ht="48">
       <c r="A13" s="78"/>
       <c r="B13" s="12" t="s">
         <v>60</v>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="AD13" s="2"/>
     </row>
-    <row r="14" spans="1:31" ht="17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" ht="17">
       <c r="A14" s="78"/>
       <c r="B14" s="12" t="s">
         <v>61</v>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="AD14" s="2"/>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31">
       <c r="H15" s="28"/>
       <c r="I15" s="29"/>
       <c r="S15" s="2"/>
@@ -6299,7 +6299,7 @@
       <c r="AD15" s="2"/>
       <c r="AE15" s="2"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31">
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
       <c r="S16" s="2"/>
@@ -6316,7 +6316,11 @@
       <c r="AD16" s="2"/>
       <c r="AE16" s="2"/>
     </row>
-    <row r="17" spans="8:31" x14ac:dyDescent="0.2">
+    <row r="17" spans="4:31">
+      <c r="D17" s="20">
+        <f>D6+D11</f>
+        <v>666</v>
+      </c>
       <c r="H17" s="28"/>
       <c r="I17" s="33"/>
       <c r="J17" s="33"/>
@@ -6342,7 +6346,7 @@
       <c r="AD17" s="33"/>
       <c r="AE17" s="2"/>
     </row>
-    <row r="18" spans="8:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="4:31">
       <c r="I18" s="33"/>
       <c r="J18" s="33"/>
       <c r="K18" s="36"/>
@@ -6367,7 +6371,7 @@
       <c r="AD18" s="33"/>
       <c r="AE18" s="2"/>
     </row>
-    <row r="19" spans="8:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="4:31">
       <c r="I19" s="34"/>
       <c r="J19" s="34"/>
       <c r="S19" s="34"/>
@@ -6377,7 +6381,7 @@
       <c r="Z19" s="34"/>
       <c r="AE19" s="2"/>
     </row>
-    <row r="20" spans="8:31" x14ac:dyDescent="0.2">
+    <row r="20" spans="4:31">
       <c r="I20" s="34"/>
       <c r="J20" s="34"/>
       <c r="S20" s="34"/>
@@ -6387,7 +6391,7 @@
       <c r="Z20" s="34"/>
       <c r="AE20" s="2"/>
     </row>
-    <row r="21" spans="8:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="4:31">
       <c r="I21" s="34"/>
       <c r="J21" s="34"/>
       <c r="S21" s="34"/>
@@ -6397,12 +6401,36 @@
       <c r="Z21" s="34"/>
       <c r="AE21" s="2"/>
     </row>
-    <row r="22" spans="8:31" x14ac:dyDescent="0.2">
-      <c r="I22" s="34"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
+    <row r="22" spans="4:31">
+      <c r="F22" s="19">
+        <f>F7*10</f>
+        <v>-40.821010000000001</v>
+      </c>
+      <c r="G22" s="19">
+        <f t="shared" ref="G22:L22" si="7">G7*10</f>
+        <v>-22.351925000000001</v>
+      </c>
+      <c r="H22" s="19">
+        <f t="shared" si="7"/>
+        <v>-17.639506000000001</v>
+      </c>
+      <c r="I22" s="19">
+        <f t="shared" si="7"/>
+        <v>-5.4773069999999997</v>
+      </c>
+      <c r="J22" s="19">
+        <f t="shared" si="7"/>
+        <v>-2.5381290000000001</v>
+      </c>
+      <c r="K22" s="19">
+        <f t="shared" si="7"/>
+        <v>-0.37968540000000001</v>
+      </c>
+      <c r="L22" s="19">
+        <f t="shared" si="7"/>
+        <v>-3.6013289999999998</v>
+      </c>
+      <c r="M22" s="54"/>
       <c r="N22" s="32"/>
       <c r="O22" s="32"/>
       <c r="P22" s="32"/>
@@ -6422,7 +6450,36 @@
       <c r="AD22" s="32"/>
       <c r="AE22" s="2"/>
     </row>
-    <row r="23" spans="8:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="4:31">
+      <c r="F23" s="19">
+        <f t="shared" ref="F23:L23" si="8">F8*10</f>
+        <v>-55.832639999999998</v>
+      </c>
+      <c r="G23" s="19">
+        <f t="shared" si="8"/>
+        <v>-5.0711309999999994</v>
+      </c>
+      <c r="H23" s="19">
+        <f t="shared" si="8"/>
+        <v>3.0180359999999999</v>
+      </c>
+      <c r="I23" s="19">
+        <f t="shared" si="8"/>
+        <v>3.6792799999999999</v>
+      </c>
+      <c r="J23" s="19">
+        <f t="shared" si="8"/>
+        <v>-1.034324</v>
+      </c>
+      <c r="K23" s="19">
+        <f t="shared" si="8"/>
+        <v>-1.1332751999999999</v>
+      </c>
+      <c r="L23" s="19">
+        <f t="shared" si="8"/>
+        <v>-7.4670210000000008</v>
+      </c>
+      <c r="M23" s="19"/>
       <c r="S23" s="2"/>
       <c r="T23" s="34"/>
       <c r="U23" s="34"/>
@@ -6436,7 +6493,36 @@
       <c r="AD23" s="2"/>
       <c r="AE23" s="2"/>
     </row>
-    <row r="24" spans="8:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="4:31">
+      <c r="F24" s="19">
+        <f t="shared" ref="F24:L24" si="9">F9*10</f>
+        <v>-64.346069999999997</v>
+      </c>
+      <c r="G24" s="19">
+        <f t="shared" si="9"/>
+        <v>-43.490003000000002</v>
+      </c>
+      <c r="H24" s="19">
+        <f t="shared" si="9"/>
+        <v>-2.0266600000000001</v>
+      </c>
+      <c r="I24" s="19">
+        <f t="shared" si="9"/>
+        <v>7.3443970000000007</v>
+      </c>
+      <c r="J24" s="19">
+        <f t="shared" si="9"/>
+        <v>-2.1377350000000002</v>
+      </c>
+      <c r="K24" s="19">
+        <f t="shared" si="9"/>
+        <v>-0.86318059999999996</v>
+      </c>
+      <c r="L24" s="19">
+        <f t="shared" si="9"/>
+        <v>-11.026009000000002</v>
+      </c>
+      <c r="M24" s="19"/>
       <c r="S24" s="2"/>
       <c r="T24" s="34"/>
       <c r="U24" s="32"/>
@@ -6450,7 +6536,36 @@
       <c r="AD24" s="2"/>
       <c r="AE24" s="2"/>
     </row>
-    <row r="25" spans="8:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="4:31">
+      <c r="F25" s="19">
+        <f t="shared" ref="F25:L25" si="10">F10*10</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="19">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="19">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="19">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="19">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="19">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="19">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="19"/>
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
@@ -6463,6 +6578,202 @@
       <c r="AB25" s="57"/>
       <c r="AD25" s="2"/>
       <c r="AE25" s="2"/>
+    </row>
+    <row r="26" spans="4:31">
+      <c r="F26" s="19">
+        <f t="shared" ref="F26:L26" si="11">F11*10</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="19">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="19">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="19">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="19">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="19">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="19">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="19"/>
+    </row>
+    <row r="27" spans="4:31">
+      <c r="F27" s="19">
+        <f t="shared" ref="F27:L27" si="12">F12*10</f>
+        <v>-56.891949999999994</v>
+      </c>
+      <c r="G27" s="19">
+        <f t="shared" si="12"/>
+        <v>-51.104610000000001</v>
+      </c>
+      <c r="H27" s="19">
+        <f t="shared" si="12"/>
+        <v>-18.663228</v>
+      </c>
+      <c r="I27" s="19">
+        <f t="shared" si="12"/>
+        <v>9.8354250000000008</v>
+      </c>
+      <c r="J27" s="19">
+        <f t="shared" si="12"/>
+        <v>-2.924115</v>
+      </c>
+      <c r="K27" s="19">
+        <f t="shared" si="12"/>
+        <v>-1.5133083000000001</v>
+      </c>
+      <c r="L27" s="19">
+        <f t="shared" si="12"/>
+        <v>-9.9440299999999997</v>
+      </c>
+      <c r="M27" s="19"/>
+    </row>
+    <row r="28" spans="4:31">
+      <c r="F28" s="19">
+        <f t="shared" ref="F28:L28" si="13">F13*10</f>
+        <v>-68.943029999999993</v>
+      </c>
+      <c r="G28" s="19">
+        <f t="shared" si="13"/>
+        <v>3.067726</v>
+      </c>
+      <c r="H28" s="19">
+        <f t="shared" si="13"/>
+        <v>11.824392</v>
+      </c>
+      <c r="I28" s="19">
+        <f t="shared" si="13"/>
+        <v>2.1743540000000001</v>
+      </c>
+      <c r="J28" s="19">
+        <f t="shared" si="13"/>
+        <v>-2.462218</v>
+      </c>
+      <c r="K28" s="19">
+        <f t="shared" si="13"/>
+        <v>-0.92344439999999994</v>
+      </c>
+      <c r="L28" s="19">
+        <f t="shared" si="13"/>
+        <v>-10.680924999999998</v>
+      </c>
+      <c r="M28" s="19"/>
+    </row>
+    <row r="29" spans="4:31">
+      <c r="F29" s="19">
+        <f t="shared" ref="F29:L29" si="14">F14*10</f>
+        <v>-78.111260000000001</v>
+      </c>
+      <c r="G29" s="19">
+        <f t="shared" si="14"/>
+        <v>-38.320028999999998</v>
+      </c>
+      <c r="H29" s="19">
+        <f t="shared" si="14"/>
+        <v>-3.6974020000000003</v>
+      </c>
+      <c r="I29" s="19">
+        <f t="shared" si="14"/>
+        <v>1.8944879999999999</v>
+      </c>
+      <c r="J29" s="19">
+        <f t="shared" si="14"/>
+        <v>-4.1502340000000002</v>
+      </c>
+      <c r="K29" s="19">
+        <f t="shared" si="14"/>
+        <v>-1.4343163999999999</v>
+      </c>
+      <c r="L29" s="19">
+        <f t="shared" si="14"/>
+        <v>-2.2289590000000001</v>
+      </c>
+      <c r="M29" s="19"/>
+    </row>
+    <row r="30" spans="4:31">
+      <c r="F30" s="19">
+        <f t="shared" ref="F30:L30" si="15">F15*10</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="19">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="19">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="19">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="19">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="19">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="19">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="19"/>
+    </row>
+    <row r="31" spans="4:31">
+      <c r="F31" s="19">
+        <f t="shared" ref="F31:L31" si="16">F16*10</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="19">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="19">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="19">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="19">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="19">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="19">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M31" s="19"/>
+    </row>
+    <row r="32" spans="4:31">
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6479,12 +6790,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{519C11FF-7B8B-444D-A4F9-FC7EAF37751C}">
   <dimension ref="A1:H52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" s="26"/>
       <c r="B1" s="26" t="s">
         <v>83</v>
@@ -6508,7 +6819,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
@@ -6534,7 +6845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="A3" s="26" t="s">
         <v>1</v>
       </c>
@@ -6560,7 +6871,7 @@
         <v>5.8822429149785202E-9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8">
       <c r="A4" s="26" t="s">
         <v>2</v>
       </c>
@@ -6586,7 +6897,7 @@
         <v>6.0279373914617896E-7</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8">
       <c r="A5" s="26" t="s">
         <v>3</v>
       </c>
@@ -6612,7 +6923,7 @@
         <v>3.6157114420322503E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8">
       <c r="A6" s="26" t="s">
         <v>4</v>
       </c>
@@ -6638,7 +6949,7 @@
         <v>2.1666299047762301E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8">
       <c r="A7" s="26" t="s">
         <v>5</v>
       </c>
@@ -6664,7 +6975,7 @@
         <v>1.30415805791173E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8">
       <c r="A8" s="26" t="s">
         <v>6</v>
       </c>
@@ -6690,7 +7001,7 @@
         <v>3.5481616786991999E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8">
       <c r="A9" s="26" t="s">
         <v>7</v>
       </c>
@@ -6716,7 +7027,7 @@
         <v>1.63264024521936E-9</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8">
       <c r="A10" s="26" t="s">
         <v>8</v>
       </c>
@@ -6742,7 +7053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8">
       <c r="A11" s="26" t="s">
         <v>9</v>
       </c>
@@ -6768,7 +7079,7 @@
         <v>0.23525886487537301</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8">
       <c r="A12" s="26" t="s">
         <v>10</v>
       </c>
@@ -6794,7 +7105,7 @@
         <v>2.2535603312334699E-6</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8">
       <c r="A13" s="26" t="s">
         <v>11</v>
       </c>
@@ -6820,7 +7131,7 @@
         <v>1.57892081157152E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8">
       <c r="A14" s="26" t="s">
         <v>12</v>
       </c>
@@ -6846,7 +7157,7 @@
         <v>1.83588878510665E-5</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8">
       <c r="A15" s="26" t="s">
         <v>13</v>
       </c>
@@ -6872,7 +7183,7 @@
         <v>7.45437928761916E-6</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8">
       <c r="A16" s="26" t="s">
         <v>14</v>
       </c>
@@ -6898,7 +7209,7 @@
         <v>1.0772508720613399E-6</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8">
       <c r="A17" s="26" t="s">
         <v>15</v>
       </c>
@@ -6924,7 +7235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8">
       <c r="A18" s="26" t="s">
         <v>22</v>
       </c>
@@ -6950,7 +7261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8">
       <c r="A19" s="26" t="s">
         <v>23</v>
       </c>
@@ -6976,7 +7287,7 @@
         <v>2.90985350500428E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8">
       <c r="A20" s="26" t="s">
         <v>24</v>
       </c>
@@ -7002,7 +7313,7 @@
         <v>0.88340437010588002</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8">
       <c r="A21" s="26" t="s">
         <v>25</v>
       </c>
@@ -7028,7 +7339,7 @@
         <v>7.0378497831290895E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8">
       <c r="A22" s="26" t="s">
         <v>26</v>
       </c>
@@ -7054,7 +7365,7 @@
         <v>3.6429685934535899E-9</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8">
       <c r="A23" s="26" t="s">
         <v>27</v>
       </c>
@@ -7080,7 +7391,7 @@
         <v>8.2405128298823595E-7</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8">
       <c r="A24" s="26" t="s">
         <v>28</v>
       </c>
@@ -7106,7 +7417,7 @@
         <v>2.6962533357340199E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8">
       <c r="A25" s="26" t="s">
         <v>29</v>
       </c>
@@ -7132,7 +7443,7 @@
         <v>5.0182080713057101E-14</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8">
       <c r="A26" s="26" t="s">
         <v>16</v>
       </c>
@@ -7158,7 +7469,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8">
       <c r="A27" s="26" t="s">
         <v>17</v>
       </c>
@@ -7184,7 +7495,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8">
       <c r="A28" s="26" t="s">
         <v>18</v>
       </c>
@@ -7210,7 +7521,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8">
       <c r="A29" s="26" t="s">
         <v>71</v>
       </c>
@@ -7236,7 +7547,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8">
       <c r="A30" s="26" t="s">
         <v>90</v>
       </c>
@@ -7262,7 +7573,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8">
       <c r="A31" s="26" t="s">
         <v>91</v>
       </c>
@@ -7288,7 +7599,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8">
       <c r="A32" s="26" t="s">
         <v>92</v>
       </c>
@@ -7314,7 +7625,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8">
       <c r="A33" s="26" t="s">
         <v>93</v>
       </c>
@@ -7340,7 +7651,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8">
       <c r="A34" s="26" t="s">
         <v>122</v>
       </c>
@@ -7366,7 +7677,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8">
       <c r="A35" s="26" t="s">
         <v>19</v>
       </c>
@@ -7392,7 +7703,7 @@
         <v>0.14902670735124601</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8">
       <c r="A36" s="26" t="s">
         <v>20</v>
       </c>
@@ -7418,7 +7729,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8">
       <c r="A37" s="26" t="s">
         <v>21</v>
       </c>
@@ -7444,7 +7755,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8">
       <c r="A38" s="26" t="s">
         <v>72</v>
       </c>
@@ -7470,7 +7781,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8">
       <c r="A39" s="26" t="s">
         <v>94</v>
       </c>
@@ -7496,7 +7807,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8">
       <c r="A40" s="26" t="s">
         <v>95</v>
       </c>
@@ -7522,7 +7833,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8">
       <c r="A41" s="26" t="s">
         <v>96</v>
       </c>
@@ -7548,7 +7859,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8">
       <c r="A42" s="26" t="s">
         <v>97</v>
       </c>
@@ -7574,7 +7885,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:8" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" s="73" customFormat="1">
       <c r="A43" s="67" t="s">
         <v>123</v>
       </c>
@@ -7600,7 +7911,7 @@
         <v>0.99341584382400705</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8">
       <c r="A44" s="26" t="s">
         <v>30</v>
       </c>
@@ -7626,7 +7937,7 @@
         <v>4.0553701508017097E-8</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8">
       <c r="A45" s="26" t="s">
         <v>31</v>
       </c>
@@ -7652,7 +7963,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8">
       <c r="A46" s="26" t="s">
         <v>32</v>
       </c>
@@ -7678,7 +7989,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8">
       <c r="A47" s="26" t="s">
         <v>98</v>
       </c>
@@ -7704,7 +8015,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8">
       <c r="A48" s="26" t="s">
         <v>73</v>
       </c>
@@ -7730,7 +8041,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8">
       <c r="A49" s="26" t="s">
         <v>99</v>
       </c>
@@ -7756,7 +8067,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8">
       <c r="A50" s="26" t="s">
         <v>100</v>
       </c>
@@ -7782,7 +8093,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8">
       <c r="A51" s="26" t="s">
         <v>101</v>
       </c>
@@ -7808,7 +8119,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:8" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" s="73" customFormat="1">
       <c r="A52" s="67" t="s">
         <v>124</v>
       </c>
@@ -7842,7 +8153,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BA101E-0096-4443-A5B7-9E57B2948D53}">
   <dimension ref="A1:Z21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.1640625" style="17" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="17"/>
@@ -7860,7 +8171,7 @@
     <col min="26" max="16384" width="10.83203125" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="7" customFormat="1" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" s="7" customFormat="1" ht="41" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -7889,7 +8200,7 @@
       <c r="X1" s="55"/>
       <c r="Y1" s="52"/>
     </row>
-    <row r="2" spans="1:26" s="7" customFormat="1" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" s="7" customFormat="1" ht="68" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>38</v>
       </c>
@@ -7961,7 +8272,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="8" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" s="8" customFormat="1" ht="40" customHeight="1">
       <c r="B3" s="9"/>
       <c r="C3" s="10"/>
       <c r="D3" s="11"/>
@@ -7993,7 +8304,7 @@
       <c r="X3" s="11"/>
       <c r="Y3" s="9"/>
     </row>
-    <row r="4" spans="1:26" s="8" customFormat="1" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" s="8" customFormat="1" ht="40" hidden="1" customHeight="1">
       <c r="B4" s="9"/>
       <c r="C4" s="10"/>
       <c r="D4" s="11"/>
@@ -8010,7 +8321,7 @@
       <c r="X4" s="11"/>
       <c r="Y4" s="9"/>
     </row>
-    <row r="5" spans="1:26" s="13" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" s="13" customFormat="1" ht="34" hidden="1">
       <c r="A5" s="12" t="s">
         <v>50</v>
       </c>
@@ -8060,7 +8371,7 @@
       <c r="X5" s="57"/>
       <c r="Y5" s="16"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26">
       <c r="A6" s="30" t="s">
         <v>102</v>
       </c>
@@ -8082,7 +8393,7 @@
       <c r="T6" s="40"/>
       <c r="U6" s="40"/>
     </row>
-    <row r="7" spans="1:26" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="70" customHeight="1">
       <c r="A7" s="78" t="s">
         <v>104</v>
       </c>
@@ -8158,7 +8469,7 @@
         <v>1.707921</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" ht="65" customHeight="1">
       <c r="A8" s="78"/>
       <c r="B8" s="12" t="s">
         <v>60</v>
@@ -8233,7 +8544,7 @@
       </c>
       <c r="Z8" s="79"/>
     </row>
-    <row r="9" spans="1:26" ht="78" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="78" customHeight="1">
       <c r="A9" s="78"/>
       <c r="B9" s="12" t="s">
         <v>61</v>
@@ -8308,7 +8619,7 @@
       </c>
       <c r="Z9" s="79"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26">
       <c r="H11" s="28"/>
       <c r="I11" s="29"/>
       <c r="O11" s="2"/>
@@ -8323,7 +8634,7 @@
       <c r="X11" s="57"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26">
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
       <c r="O12" s="2"/>
@@ -8339,7 +8650,7 @@
       <c r="Y12" s="53"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26">
       <c r="H13" s="28"/>
       <c r="I13" s="33"/>
       <c r="J13" s="33"/>
@@ -8360,7 +8671,7 @@
       <c r="Y13" s="36"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26">
       <c r="I14" s="33"/>
       <c r="J14" s="33"/>
       <c r="K14" s="36"/>
@@ -8380,7 +8691,7 @@
       <c r="Y14" s="36"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26">
       <c r="F15" s="36"/>
       <c r="G15" s="36"/>
       <c r="H15" s="36"/>
@@ -8400,7 +8711,7 @@
       <c r="V15" s="34"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26">
       <c r="F16" s="36"/>
       <c r="G16" s="36"/>
       <c r="H16" s="36"/>
@@ -8420,7 +8731,7 @@
       <c r="V16" s="34"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="6:26" x14ac:dyDescent="0.2">
+    <row r="17" spans="6:26">
       <c r="F17" s="37"/>
       <c r="G17" s="37"/>
       <c r="R17" s="17"/>
@@ -8430,7 +8741,7 @@
       <c r="V17" s="34"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="6:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="6:26">
       <c r="F18" s="37"/>
       <c r="G18" s="37"/>
       <c r="R18" s="17"/>
@@ -8443,7 +8754,7 @@
       <c r="Y18" s="54"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="6:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="6:26">
       <c r="F19" s="37"/>
       <c r="G19" s="37"/>
       <c r="R19" s="17"/>
@@ -8455,7 +8766,7 @@
       <c r="X19" s="57"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="6:26" x14ac:dyDescent="0.2">
+    <row r="20" spans="6:26">
       <c r="F20" s="37"/>
       <c r="G20" s="54"/>
       <c r="H20" s="54"/>
@@ -8477,7 +8788,7 @@
       <c r="X20" s="57"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" spans="6:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="6:26">
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
@@ -8504,12 +8815,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F87241B1-EEA4-9644-98C8-8514E386A931}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="87.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="34">
       <c r="B1" s="12" t="s">
         <v>44</v>
       </c>
@@ -8517,7 +8828,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="16">
       <c r="A2" s="25" t="s">
         <v>63</v>
       </c>
@@ -8525,7 +8836,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="16">
       <c r="A3" s="25" t="s">
         <v>64</v>
       </c>
@@ -8533,7 +8844,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="16">
       <c r="A4" s="25" t="s">
         <v>65</v>
       </c>
@@ -8541,7 +8852,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="16">
       <c r="A5" s="25" t="s">
         <v>66</v>
       </c>
@@ -8549,7 +8860,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="16">
       <c r="A6" s="25" t="s">
         <v>67</v>
       </c>
@@ -8557,7 +8868,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="16">
       <c r="A7" s="25" t="s">
         <v>68</v>
       </c>
